--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487601_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487601_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6336</v>
+        <v>4.9607</v>
       </c>
       <c r="E2" t="n">
         <v>2.4163</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2173</v>
+        <v>2.5444</v>
       </c>
       <c r="G2" t="n">
         <v>3.4742</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8004</v>
+        <v>-0.4733</v>
       </c>
       <c r="T2" t="n">
         <v>-0.4845</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3158</v>
+        <v>0.0112</v>
       </c>
       <c r="V2" t="n">
         <v>0.9896</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>D. BUTUNOI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9035</v>
+        <v>0.3439</v>
       </c>
       <c r="E3" t="n">
-        <v>0.795</v>
+        <v>-0.9689</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1086</v>
+        <v>1.3128</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.4224</v>
+        <v>0.8626</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0076</v>
+        <v>0.8626</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4148</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1265</v>
+        <v>0.0618</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0453</v>
+        <v>0.0618</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08119999999999999</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5489</v>
+        <v>0.8008</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0529</v>
+        <v>0.8008</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.496</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7463</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7584</v>
+        <v>0.0634</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6684</v>
+        <v>-0.0606</v>
       </c>
       <c r="U3" t="n">
-        <v>1.09</v>
+        <v>0.1239</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1788</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. BUTUNOI</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3711</v>
+        <v>0.0533</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9689</v>
+        <v>0.2883</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3401</v>
+        <v>-0.2349</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8626</v>
+        <v>1.0385</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8626</v>
+        <v>1.5835</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0.545</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0618</v>
+        <v>1.4006</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0618</v>
+        <v>1.4006</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8008</v>
+        <v>-0.3621</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8008</v>
+        <v>0.1829</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.545</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0906</v>
+        <v>-0.0031</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0606</v>
+        <v>-0.1422</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1512</v>
+        <v>0.1391</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.1761</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2103</v>
+        <v>-0.2333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1882</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3985</v>
+        <v>-0.3275</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0385</v>
+        <v>-2.4224</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5835</v>
+        <v>-1.0076</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.545</v>
+        <v>-1.4148</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4006</v>
+        <v>0.1265</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4006</v>
+        <v>0.0453</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3621</v>
+        <v>-2.5489</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1829</v>
+        <v>-1.0529</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.545</v>
+        <v>-1.496</v>
       </c>
       <c r="P5" t="n">
-        <v>0.194</v>
+        <v>1.7463</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2667</v>
+        <v>0.6216</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2423</v>
+        <v>-0.0323</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0244</v>
+        <v>0.6539</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1761</v>
+        <v>-0.1788</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1761</v>
+        <v>-0.1788</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0027</v>
+        <v>-0.848</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.6137</v>
+        <v>-2.046</v>
       </c>
       <c r="F6" t="n">
-        <v>2.611</v>
+        <v>1.198</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.485</v>
+        <v>2.1119</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.638</v>
+        <v>2.7558</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.847</v>
+        <v>-0.644</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.509</v>
+        <v>3.6157</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.4963</v>
+        <v>3.0195</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0127</v>
+        <v>0.5962</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9759</v>
+        <v>-1.5038</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1417</v>
+        <v>-0.2637</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-1.2402</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9702</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9403</v>
+        <v>-4.8508</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9105</v>
+        <v>2.5224</v>
       </c>
       <c r="S6" t="n">
-        <v>1.079</v>
+        <v>-0.0673</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0584</v>
+        <v>-0.8109</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1373</v>
+        <v>0.7436</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4331</v>
+        <v>-0.5642</v>
       </c>
       <c r="W6" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4609</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>A. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0848</v>
+        <v>-1.0114</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4464</v>
+        <v>-0.143</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3616</v>
+        <v>-0.8683</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1119</v>
+        <v>-1.1329</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7558</v>
+        <v>-0.0428</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.644</v>
+        <v>-1.09</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6157</v>
+        <v>0.0412</v>
       </c>
       <c r="K7" t="n">
-        <v>3.0195</v>
+        <v>0.0412</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5962</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5038</v>
+        <v>-1.174</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2637</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2402</v>
+        <v>-1.09</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3284</v>
+        <v>0.5821</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8508</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5224</v>
+        <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3042</v>
+        <v>-0.2818</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2113</v>
+        <v>-0.1842</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9072</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5642</v>
+        <v>-0.1788</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5642</v>
+        <v>-0.1788</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ALMENARA SANABRIAS</t>
+          <t>E. CALVO SALVE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3117</v>
+        <v>-1.3506</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4433</v>
+        <v>-2.4178</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8683</v>
+        <v>1.0673</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1329</v>
+        <v>1.5108</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0428</v>
+        <v>2.2121</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.09</v>
+        <v>-0.7013</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0412</v>
+        <v>1.5677</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0412</v>
+        <v>2.1132</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.5455</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.174</v>
+        <v>-0.0569</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.0989</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.09</v>
+        <v>-0.1557</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5821</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.8806</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5821</v>
+        <v>2.3284</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5821</v>
+        <v>0.1968</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4845</v>
+        <v>-0.387</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09760000000000001</v>
+        <v>0.5838</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1788</v>
+        <v>-1.506</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1788</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. CALVO SALVE</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1598</v>
+        <v>-1.6757</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8182</v>
+        <v>-4.0141</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6584</v>
+        <v>2.3384</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5108</v>
+        <v>-3.485</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2121</v>
+        <v>-2.638</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7013</v>
+        <v>-0.847</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5677</v>
+        <v>-2.509</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1132</v>
+        <v>-2.4963</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5455</v>
+        <v>-0.0127</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0569</v>
+        <v>-0.9759</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0989</v>
+        <v>-0.1417</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1557</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5523</v>
+        <v>0.9702</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3284</v>
+        <v>2.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0.406</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7874</v>
+        <v>-0.4588</v>
       </c>
       <c r="U9" t="n">
-        <v>0.175</v>
+        <v>0.8648</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.506</v>
+        <v>0.4331</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.788</v>
+        <v>-0.4609</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5469</v>
+        <v>-1.7738</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7397</v>
+        <v>-1.2392</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8071</v>
+        <v>-0.5346</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5872000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>2.3284</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8973</v>
+        <v>-0.1242</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1508</v>
+        <v>-0.6503</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2535</v>
+        <v>0.526</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4504</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5406</v>
+        <v>-4.5411</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8909</v>
+        <v>-6.5916</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3503</v>
+        <v>2.0505</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6681</v>
@@ -1312,13 +1312,13 @@
         <v>2.3284</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2425</v>
+        <v>0.242</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4262</v>
+        <v>-0.2745</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8163</v>
+        <v>0.5165</v>
       </c>
       <c r="V11" t="n">
         <v>0.3776</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0322</v>
+        <v>-4.9049</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0417</v>
+        <v>-3.9416</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9905</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0033</v>
@@ -1390,13 +1390,13 @@
         <v>0.194</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1635</v>
+        <v>-0.0362</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1788</v>
@@ -1423,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.9808</v>
+        <v>-10.9809</v>
       </c>
       <c r="E13" t="n">
         <v>-18.5633</v>
@@ -1468,13 +1468,13 @@
         <v>18.4331</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5438999999999998</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>-3.5669</v>
       </c>
       <c r="U13" t="n">
-        <v>4.1109</v>
+        <v>4.1106</v>
       </c>
       <c r="V13" t="n">
         <v>-3.432799999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2916</v>
+        <v>6.0101</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2419</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>5.0497</v>
+        <v>5.2677</v>
       </c>
       <c r="G14" t="n">
         <v>1.7595</v>
@@ -1546,13 +1546,13 @@
         <v>4.2687</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9336</v>
+        <v>-0.2151</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1508</v>
+        <v>-0.6503</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2172</v>
+        <v>0.4352</v>
       </c>
       <c r="V14" t="n">
         <v>3.1075</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1731</v>
+        <v>2.7311</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.268</v>
+        <v>-1.2824</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4411</v>
+        <v>4.0135</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5503</v>
+        <v>0.4805</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1147</v>
+        <v>-2.4658</v>
       </c>
       <c r="I15" t="n">
-        <v>1.665</v>
+        <v>2.9463</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9999</v>
+        <v>0.3438</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4573</v>
+        <v>-1.6683</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5427</v>
+        <v>2.0121</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4496</v>
+        <v>0.1367</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.572</v>
+        <v>-0.7975</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1223</v>
+        <v>0.9343</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9702</v>
+        <v>2.7164</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>3.8806</v>
+        <v>3.6866</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4661</v>
+        <v>-0.4181</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.544</v>
+        <v>-0.6082</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0101</v>
+        <v>0.1901</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1865</v>
+        <v>-0.0478</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1865</v>
+        <v>-0.0478</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0765</v>
+        <v>1.7098</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5827</v>
+        <v>-1.268</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6592</v>
+        <v>2.9778</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4805</v>
+        <v>0.5503</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.4658</v>
+        <v>-1.1147</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9463</v>
+        <v>1.665</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3438</v>
+        <v>1.9999</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6683</v>
+        <v>0.4573</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0121</v>
+        <v>1.5427</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1367</v>
+        <v>-1.4496</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7975</v>
+        <v>-1.572</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9343</v>
+        <v>0.1223</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7164</v>
+        <v>0.9702</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R16" t="n">
-        <v>3.6866</v>
+        <v>3.8806</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0727</v>
+        <v>0.0028</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9085</v>
+        <v>-0.544</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1642</v>
+        <v>0.5468</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0478</v>
+        <v>0.1865</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0478</v>
+        <v>0.1865</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6242</v>
+        <v>1.6787</v>
       </c>
       <c r="E17" t="n">
         <v>1.0292</v>
       </c>
       <c r="F17" t="n">
-        <v>0.595</v>
+        <v>0.6495</v>
       </c>
       <c r="G17" t="n">
         <v>0.8117</v>
@@ -1780,13 +1780,13 @@
         <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.44</v>
+        <v>1.1942</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5047</v>
+        <v>0.2044</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9353</v>
+        <v>0.9898</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1856</v>
@@ -1858,13 +1858,13 @@
         <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4614</v>
+        <v>0.2156</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1222</v>
+        <v>-0.1781</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3392</v>
+        <v>0.3937</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERNANDEZ</t>
+          <t>I. MENCARA JIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0487</v>
+        <v>1.0196</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9457</v>
+        <v>-0.9702</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.897</v>
+        <v>1.9898</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7974</v>
+        <v>1.2444</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3347</v>
+        <v>-0.4951</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4627</v>
+        <v>1.7396</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8244</v>
+        <v>1.3571</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6776</v>
+        <v>0.0124</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1468</v>
+        <v>1.3447</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.027</v>
+        <v>-0.1127</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3429</v>
+        <v>-0.5075</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.3948</v>
       </c>
       <c r="P19" t="n">
         <v>-0.3881</v>
@@ -1936,28 +1936,28 @@
         <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5334</v>
+        <v>-0.1666</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0617</v>
+        <v>-0.387</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4718</v>
+        <v>0.2204</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.894</v>
+        <v>0.3299</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.894</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FERNÁNDEZ GÓMEZ</t>
+          <t>J. JIMENEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.794</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.427</v>
+        <v>1.7455</v>
       </c>
       <c r="F20" t="n">
-        <v>1.359</v>
+        <v>-0.9515</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0198</v>
+        <v>1.7974</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5750999999999999</v>
+        <v>1.3347</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4448</v>
+        <v>0.4627</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3752</v>
+        <v>3.8244</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9969</v>
+        <v>2.6776</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6217</v>
+        <v>1.1468</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.395</v>
+        <v>-2.027</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.572</v>
+        <v>-1.3429</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1642</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1045</v>
+        <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6011</v>
+        <v>0.2787</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6695</v>
+        <v>-0.1385</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9316</v>
+        <v>0.4172</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1865</v>
+        <v>-0.894</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4686</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MENCARA JIMENEZ</t>
+          <t>A. FERNÁNDEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4285</v>
+        <v>-0.2959</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3706</v>
+        <v>-1.3278</v>
       </c>
       <c r="F21" t="n">
-        <v>1.799</v>
+        <v>1.0319</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2444</v>
+        <v>-2.0198</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4951</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7396</v>
+        <v>-1.4448</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3571</v>
+        <v>0.3752</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0124</v>
+        <v>0.9969</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3447</v>
+        <v>-0.6217</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1127</v>
+        <v>-2.395</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5075</v>
+        <v>-1.572</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3948</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5523</v>
+        <v>3.1045</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7577</v>
+        <v>0.3732</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7874</v>
+        <v>-0.2314</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0296</v>
+        <v>0.6046</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3299</v>
+        <v>0.1865</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.4686</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3299</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4983</v>
+        <v>-0.3436</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5657</v>
+        <v>-0.4656</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0675</v>
+        <v>0.122</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1565</v>
@@ -2170,13 +2170,13 @@
         <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2059</v>
+        <v>-0.0513</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2423</v>
+        <v>-0.1422</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0.2821</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.584</v>
+        <v>-1.193</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3463</v>
+        <v>-0.1461</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2376</v>
+        <v>-1.0469</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8968</v>
@@ -2248,13 +2248,13 @@
         <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7454</v>
+        <v>-0.3544</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6057</v>
+        <v>-0.4055</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1397</v>
+        <v>0.051</v>
       </c>
       <c r="V23" t="n">
         <v>0.2821</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9517</v>
+        <v>-2.3244</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7442</v>
+        <v>-5.8443</v>
       </c>
       <c r="F24" t="n">
-        <v>3.7925</v>
+        <v>3.5199</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0843</v>
@@ -2326,13 +2326,13 @@
         <v>3.8806</v>
       </c>
       <c r="S24" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.2997</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7257</v>
+        <v>-0.8258</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7986</v>
+        <v>0.526</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2362,10 +2362,10 @@
         <v>10.9806</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.583</v>
+        <v>-7.5829</v>
       </c>
       <c r="F25" t="n">
-        <v>18.5637</v>
+        <v>18.5635</v>
       </c>
       <c r="G25" t="n">
         <v>1.3008</v>
@@ -2389,7 +2389,7 @@
         <v>-10.0887</v>
       </c>
       <c r="N25" t="n">
-        <v>-9.309899999999997</v>
+        <v>-9.309899999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-0.7786999999999999</v>
@@ -2404,13 +2404,13 @@
         <v>25.2241</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5441000000000001</v>
+        <v>-0.5441</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.111000000000001</v>
+        <v>-4.111</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5668</v>
+        <v>3.5666</v>
       </c>
       <c r="V25" t="n">
         <v>3.432799999999999</v>
@@ -2419,7 +2419,7 @@
         <v>3.5715</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1387</v>
+        <v>-0.1386999999999998</v>
       </c>
     </row>
   </sheetData>
